--- a/Control_Insumos.xlsx
+++ b/Control_Insumos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\STREAMLIT WEB\ANALISIS INSUMOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7BD5EC4-31A3-4740-9979-E24E37059A56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14A2C405-BA56-4A9F-84AE-ECEF6CF6AFF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="71">
   <si>
     <t>GENERACIÓN DE RESIDUOS</t>
   </si>
@@ -351,7 +351,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -406,6 +406,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -624,7 +630,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -750,6 +756,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="42" fontId="0" fillId="11" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda [0]" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -4664,7 +4671,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tblFactSolped" displayName="tblFactSolped" ref="A1:F111" dataDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tblFactSolped" displayName="tblFactSolped" ref="A1:F122" dataDxfId="6">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Año" dataDxfId="5"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Mes" dataDxfId="4"/>
@@ -6184,10 +6191,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:F111"/>
+  <dimension ref="A1:H122"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="7" width="13.81640625" customWidth="1"/>
+    <col min="8" max="8" width="9.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
@@ -7818,7 +7826,7 @@
         <v>10</v>
       </c>
       <c r="C82" s="30">
-        <v>46114</v>
+        <v>46144</v>
       </c>
       <c r="D82" s="29" t="s">
         <v>32</v>
@@ -7836,7 +7844,7 @@
         <v>10</v>
       </c>
       <c r="C83" s="30">
-        <v>46115</v>
+        <v>46144</v>
       </c>
       <c r="D83" s="29" t="s">
         <v>68</v>
@@ -7854,7 +7862,7 @@
         <v>10</v>
       </c>
       <c r="C84" s="30">
-        <v>46116</v>
+        <v>46144</v>
       </c>
       <c r="D84" s="29" t="s">
         <v>69</v>
@@ -7872,7 +7880,7 @@
         <v>10</v>
       </c>
       <c r="C85" s="30">
-        <v>46117</v>
+        <v>46144</v>
       </c>
       <c r="D85" s="29" t="s">
         <v>35</v>
@@ -7890,7 +7898,7 @@
         <v>10</v>
       </c>
       <c r="C86" s="30">
-        <v>46118</v>
+        <v>46144</v>
       </c>
       <c r="D86" s="29" t="s">
         <v>36</v>
@@ -7908,7 +7916,7 @@
         <v>11</v>
       </c>
       <c r="C87" s="30">
-        <v>46119</v>
+        <v>46180</v>
       </c>
       <c r="D87" s="29" t="s">
         <v>32</v>
@@ -7926,7 +7934,7 @@
         <v>11</v>
       </c>
       <c r="C88" s="30">
-        <v>46120</v>
+        <v>46180</v>
       </c>
       <c r="D88" s="29" t="s">
         <v>68</v>
@@ -7944,7 +7952,7 @@
         <v>11</v>
       </c>
       <c r="C89" s="30">
-        <v>46121</v>
+        <v>46180</v>
       </c>
       <c r="D89" s="29" t="s">
         <v>69</v>
@@ -7962,7 +7970,7 @@
         <v>11</v>
       </c>
       <c r="C90" s="30">
-        <v>46122</v>
+        <v>46180</v>
       </c>
       <c r="D90" s="29" t="s">
         <v>35</v>
@@ -7980,7 +7988,7 @@
         <v>11</v>
       </c>
       <c r="C91" s="30">
-        <v>46123</v>
+        <v>46180</v>
       </c>
       <c r="D91" s="29" t="s">
         <v>36</v>
@@ -7998,7 +8006,7 @@
         <v>12</v>
       </c>
       <c r="C92" s="30">
-        <v>46124</v>
+        <v>46215</v>
       </c>
       <c r="D92" s="29" t="s">
         <v>32</v>
@@ -8018,7 +8026,7 @@
         <v>12</v>
       </c>
       <c r="C93" s="30">
-        <v>46125</v>
+        <v>46215</v>
       </c>
       <c r="D93" s="29" t="s">
         <v>68</v>
@@ -8038,7 +8046,7 @@
         <v>12</v>
       </c>
       <c r="C94" s="30">
-        <v>46126</v>
+        <v>46215</v>
       </c>
       <c r="D94" s="29" t="s">
         <v>69</v>
@@ -8058,7 +8066,7 @@
         <v>12</v>
       </c>
       <c r="C95" s="30">
-        <v>46127</v>
+        <v>46215</v>
       </c>
       <c r="D95" s="29" t="s">
         <v>35</v>
@@ -8078,7 +8086,7 @@
         <v>12</v>
       </c>
       <c r="C96" s="30">
-        <v>46128</v>
+        <v>46215</v>
       </c>
       <c r="D96" s="29" t="s">
         <v>36</v>
@@ -8090,7 +8098,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A97" s="29">
         <v>2026</v>
       </c>
@@ -8098,7 +8106,7 @@
         <v>13</v>
       </c>
       <c r="C97" s="30">
-        <v>46129</v>
+        <v>46251</v>
       </c>
       <c r="D97" s="29" t="s">
         <v>32</v>
@@ -8110,7 +8118,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A98" s="29">
         <v>2026</v>
       </c>
@@ -8118,7 +8126,7 @@
         <v>13</v>
       </c>
       <c r="C98" s="30">
-        <v>46130</v>
+        <v>46251</v>
       </c>
       <c r="D98" s="29" t="s">
         <v>68</v>
@@ -8130,7 +8138,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A99" s="29">
         <v>2026</v>
       </c>
@@ -8138,7 +8146,7 @@
         <v>13</v>
       </c>
       <c r="C99" s="30">
-        <v>46131</v>
+        <v>46251</v>
       </c>
       <c r="D99" s="29" t="s">
         <v>69</v>
@@ -8150,7 +8158,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A100" s="29">
         <v>2026</v>
       </c>
@@ -8158,7 +8166,7 @@
         <v>13</v>
       </c>
       <c r="C100" s="30">
-        <v>46132</v>
+        <v>46251</v>
       </c>
       <c r="D100" s="29" t="s">
         <v>35</v>
@@ -8170,7 +8178,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A101" s="29">
         <v>2026</v>
       </c>
@@ -8178,17 +8186,19 @@
         <v>13</v>
       </c>
       <c r="C101" s="30">
-        <v>46133</v>
+        <v>46251</v>
       </c>
       <c r="D101" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="E101" s="31"/>
+      <c r="E101" s="31">
+        <v>709205</v>
+      </c>
       <c r="F101" s="29" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A102" s="29">
         <v>2026</v>
       </c>
@@ -8196,19 +8206,19 @@
         <v>14</v>
       </c>
       <c r="C102" s="30">
-        <v>46134</v>
+        <v>46287</v>
       </c>
       <c r="D102" s="29" t="s">
         <v>32</v>
       </c>
       <c r="E102" s="31">
-        <v>409382</v>
+        <v>383587</v>
       </c>
       <c r="F102" s="29" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A103" s="29">
         <v>2026</v>
       </c>
@@ -8216,19 +8226,19 @@
         <v>14</v>
       </c>
       <c r="C103" s="30">
-        <v>46135</v>
+        <v>46287</v>
       </c>
       <c r="D103" s="29" t="s">
         <v>68</v>
       </c>
       <c r="E103" s="31">
-        <v>442180</v>
+        <v>528098</v>
       </c>
       <c r="F103" s="29" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A104" s="29">
         <v>2026</v>
       </c>
@@ -8236,19 +8246,19 @@
         <v>14</v>
       </c>
       <c r="C104" s="30">
-        <v>46136</v>
+        <v>46287</v>
       </c>
       <c r="D104" s="29" t="s">
         <v>69</v>
       </c>
       <c r="E104" s="31">
-        <v>88829</v>
+        <v>51741</v>
       </c>
       <c r="F104" s="29" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A105" s="29">
         <v>2026</v>
       </c>
@@ -8256,17 +8266,19 @@
         <v>14</v>
       </c>
       <c r="C105" s="30">
-        <v>46137</v>
+        <v>46287</v>
       </c>
       <c r="D105" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="E105" s="31"/>
+      <c r="E105" s="31">
+        <v>0</v>
+      </c>
       <c r="F105" s="29" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A106" s="29">
         <v>2026</v>
       </c>
@@ -8274,65 +8286,250 @@
         <v>14</v>
       </c>
       <c r="C106" s="30">
-        <v>46138</v>
+        <v>46287</v>
       </c>
       <c r="D106" s="29" t="s">
         <v>36</v>
       </c>
       <c r="E106" s="31">
-        <v>641367</v>
+        <v>763226</v>
       </c>
       <c r="F106" s="29" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A107" s="29"/>
-      <c r="B107" s="29"/>
-      <c r="C107" s="30"/>
-      <c r="D107" s="29"/>
-      <c r="E107" s="31"/>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A107" s="29">
+        <v>2026</v>
+      </c>
+      <c r="B107" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C107" s="30">
+        <v>46322</v>
+      </c>
+      <c r="D107" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="E107" s="31">
+        <v>424852</v>
+      </c>
       <c r="F107" s="29" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A108" s="29"/>
-      <c r="B108" s="29"/>
-      <c r="C108" s="30"/>
-      <c r="D108" s="29"/>
-      <c r="E108" s="31"/>
+      <c r="H107" s="53">
+        <v>750000</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A108" s="29">
+        <v>2026</v>
+      </c>
+      <c r="B108" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C108" s="30">
+        <v>46322</v>
+      </c>
+      <c r="D108" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="E108" s="31">
+        <v>505553</v>
+      </c>
       <c r="F108" s="29" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A109" s="29"/>
-      <c r="B109" s="29"/>
-      <c r="C109" s="30"/>
-      <c r="D109" s="29"/>
-      <c r="E109" s="31"/>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A109" s="29">
+        <v>2026</v>
+      </c>
+      <c r="B109" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C109" s="30">
+        <v>46322</v>
+      </c>
+      <c r="D109" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="E109" s="31">
+        <v>56772</v>
+      </c>
       <c r="F109" s="29" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A110" s="29"/>
-      <c r="B110" s="29"/>
-      <c r="C110" s="30"/>
-      <c r="D110" s="29"/>
-      <c r="E110" s="31"/>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A110" s="29">
+        <v>2026</v>
+      </c>
+      <c r="B110" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C110" s="30">
+        <v>46322</v>
+      </c>
+      <c r="D110" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="E110" s="31">
+        <v>101052</v>
+      </c>
       <c r="F110" s="29" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A111" s="29"/>
-      <c r="B111" s="29"/>
-      <c r="C111" s="30"/>
-      <c r="D111" s="29"/>
-      <c r="E111" s="31"/>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A111" s="29">
+        <v>2026</v>
+      </c>
+      <c r="B111" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C111" s="30">
+        <v>46322</v>
+      </c>
+      <c r="D111" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="E111" s="31">
+        <v>763226</v>
+      </c>
       <c r="F111" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A112" s="29">
+        <v>2026</v>
+      </c>
+      <c r="B112" s="29"/>
+      <c r="C112" s="30"/>
+      <c r="D112" s="29"/>
+      <c r="E112" s="31"/>
+      <c r="F112" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A113" s="29">
+        <v>2026</v>
+      </c>
+      <c r="B113" s="29"/>
+      <c r="C113" s="30"/>
+      <c r="D113" s="29"/>
+      <c r="E113" s="31"/>
+      <c r="F113" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A114" s="29">
+        <v>2026</v>
+      </c>
+      <c r="B114" s="29"/>
+      <c r="C114" s="30"/>
+      <c r="D114" s="29"/>
+      <c r="E114" s="31"/>
+      <c r="F114" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A115" s="29">
+        <v>2026</v>
+      </c>
+      <c r="B115" s="29"/>
+      <c r="C115" s="30"/>
+      <c r="D115" s="29"/>
+      <c r="E115" s="31"/>
+      <c r="F115" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A116" s="29">
+        <v>2026</v>
+      </c>
+      <c r="B116" s="29"/>
+      <c r="C116" s="30"/>
+      <c r="D116" s="29"/>
+      <c r="E116" s="31"/>
+      <c r="F116" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A117" s="29">
+        <v>2026</v>
+      </c>
+      <c r="B117" s="29"/>
+      <c r="C117" s="30"/>
+      <c r="D117" s="29"/>
+      <c r="E117" s="31"/>
+      <c r="F117" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A118" s="29">
+        <v>2026</v>
+      </c>
+      <c r="B118" s="29"/>
+      <c r="C118" s="30"/>
+      <c r="D118" s="29"/>
+      <c r="E118" s="31"/>
+      <c r="F118" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A119" s="29">
+        <v>2026</v>
+      </c>
+      <c r="B119" s="29"/>
+      <c r="C119" s="30"/>
+      <c r="D119" s="29"/>
+      <c r="E119" s="31"/>
+      <c r="F119" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A120" s="29">
+        <v>2026</v>
+      </c>
+      <c r="B120" s="29"/>
+      <c r="C120" s="30"/>
+      <c r="D120" s="29"/>
+      <c r="E120" s="31"/>
+      <c r="F120" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A121" s="29">
+        <v>2026</v>
+      </c>
+      <c r="B121" s="29"/>
+      <c r="C121" s="30"/>
+      <c r="D121" s="29"/>
+      <c r="E121" s="31"/>
+      <c r="F121" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A122" s="29">
+        <v>2026</v>
+      </c>
+      <c r="B122" s="29"/>
+      <c r="C122" s="30"/>
+      <c r="D122" s="29"/>
+      <c r="E122" s="31"/>
+      <c r="F122" s="29" t="s">
         <v>67</v>
       </c>
     </row>
